--- a/countries/us-gu/2015-2019.xlsx
+++ b/countries/us-gu/2015-2019.xlsx
@@ -768,9 +768,9 @@
       <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -785,26 +785,16 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>HOLD_US_603e69a6c2fabea3ab3dc2a19a2a; HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
+          <t>HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -870,7 +860,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -905,12 +895,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2019-08-24</t>
+          <t>2019-11-09</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2019-08</t>
+          <t>2019-11</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -927,116 +917,28 @@
           <t>HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Dengue virus infections§ , Dengue</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Dengue virus infections§ , Dengue</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>country:US-GU:national</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN3" t="b">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
         <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>HOLD_US_603e69a6c2fabea3ab3dc2a19a2a; HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1102,7 +1004,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1137,12 +1039,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2019-11-16</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2019-09</t>
+          <t>2019-11</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1156,32 +1058,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>HOLD_US_460638f77881c0c3f1fa61a09e06</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Dengue virus infections§ s, Dengue-like illness</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Dengue virus infections§ s, Dengue-like illness</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1189,59 +1066,6 @@
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>country:US-GU:national</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN4" t="b">
-        <v>0</v>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1249,26 +1073,16 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>HOLD_US_603e69a6c2fabea3ab3dc2a19a2a; HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
+          <t>HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1306,778 +1120,6 @@
         </is>
       </c>
       <c r="BC4" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>us-gu</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>us-gu</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Guam, United States</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>US-GU</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Guam, United States</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>D021</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>登革热</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2019-11-09</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2019-11</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>HOLD_US_603e69a6c2fabea3ab3dc2a19a2a; HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>us-gu</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>us-gu</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Guam, United States</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>US-GU</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Guam, United States</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>D021</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>登革热</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2019-11-09</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2019-11</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Dengue virus infections§ , Dengue</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Dengue virus infections§ , Dengue</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>country:US-GU:national</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>HOLD_US_603e69a6c2fabea3ab3dc2a19a2a; HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
-        </is>
-      </c>
-      <c r="AT6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>us-gu</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>us-gu</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Guam, United States</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>US-GU</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Guam, United States</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>D021</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>登革热</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2019-11-16</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2019-11</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>HOLD_US_603e69a6c2fabea3ab3dc2a19a2a; HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
-        </is>
-      </c>
-      <c r="AT7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>us-gu</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>us-gu</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Guam, United States</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>source_series_observation</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>US-GU</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Guam, United States</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>D021</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Dengue</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>登革热</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Viral</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2019-11-16</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2019-11</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Dengue virus infections§ , Dengue</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Dengue virus infections§ , Dengue</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>country:US-GU:national</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>HOLD_US_603e69a6c2fabea3ab3dc2a19a2a; HOLD_US_6d84d26bf8267ee7c01fd24194fd</t>
-        </is>
-      </c>
-      <c r="AT8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>nndss_api</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>US CDC NNDSS</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -2209,7 +1251,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2229,7 +1271,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2239,7 +1281,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
